--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487070_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487070_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1667</v>
+        <v>5.1205</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9955</v>
+        <v>5.8155</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.8289</v>
+        <v>-0.695</v>
       </c>
       <c r="G2" t="n">
         <v>4.143</v>
@@ -610,13 +610,13 @@
         <v>1.7371</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8309</v>
+        <v>0.1229</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4164</v>
+        <v>0.4035</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4145</v>
+        <v>-0.2806</v>
       </c>
       <c r="V2" t="n">
         <v>0.0825</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3325</v>
+        <v>1.3256</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6147</v>
+        <v>0.7148</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7178</v>
+        <v>0.6107</v>
       </c>
       <c r="G3" t="n">
         <v>-1.2186</v>
@@ -688,13 +688,13 @@
         <v>1.158</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4336</v>
+        <v>0.4267</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3107</v>
+        <v>0.4108</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1229</v>
+        <v>0.0159</v>
       </c>
       <c r="V3" t="n">
         <v>1.9245</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0905</v>
+        <v>-0.1063</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7236</v>
+        <v>1.0022</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.8139999999999999</v>
+        <v>-1.1085</v>
       </c>
       <c r="G4" t="n">
         <v>-0.1353</v>
@@ -766,13 +766,13 @@
         <v>2.3161</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0324</v>
+        <v>-0.0483</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5816</v>
+        <v>-0.303</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5492</v>
+        <v>0.2548</v>
       </c>
       <c r="V4" t="n">
         <v>0.6562</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1882</v>
+        <v>-0.8962</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5904</v>
+        <v>-1.1912</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4021</v>
+        <v>0.295</v>
       </c>
       <c r="G5" t="n">
         <v>-1.1179</v>
@@ -844,13 +844,13 @@
         <v>0.965</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1752</v>
+        <v>0.4673</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9188</v>
+        <v>0.318</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2564</v>
+        <v>0.1494</v>
       </c>
       <c r="V5" t="n">
         <v>-0.2456</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.7754</v>
+        <v>-1.0873</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.632</v>
+        <v>-2.1313</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8566</v>
+        <v>1.044</v>
       </c>
       <c r="G6" t="n">
         <v>-1.0307</v>
@@ -922,13 +922,13 @@
         <v>1.3511</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8851</v>
+        <v>-0.197</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4759</v>
+        <v>0.0248</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4092</v>
+        <v>-0.2218</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2456</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.1995</v>
+        <v>-1.4251</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1552</v>
+        <v>0.405</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.0443</v>
+        <v>-1.8302</v>
       </c>
       <c r="G7" t="n">
         <v>-1.8954</v>
@@ -1000,13 +1000,13 @@
         <v>1.5441</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8831</v>
+        <v>-0.1087</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8183</v>
+        <v>-0.2581</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0648</v>
+        <v>0.1494</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. VASQUEZ BAUTISTA</t>
+          <t>M. LINDE GIL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.7444</v>
+        <v>-3.2435</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1076</v>
+        <v>0.7572</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.6368</v>
+        <v>-4.0007</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.1347</v>
+        <v>-0.1943</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.3714</v>
+        <v>1.0081</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7633</v>
+        <v>-1.2024</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3865</v>
+        <v>1.7941</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.59</v>
+        <v>2.0233</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2035</v>
+        <v>-0.2291</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.7481</v>
+        <v>-1.9884</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7813</v>
+        <v>-1.0152</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9668</v>
+        <v>-0.9732</v>
       </c>
       <c r="P8" t="n">
-        <v>0.772</v>
+        <v>-0.772</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.965</v>
+        <v>-2.8951</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7371</v>
+        <v>2.1231</v>
       </c>
       <c r="S8" t="n">
-        <v>1.6882</v>
+        <v>-0.1897</v>
       </c>
       <c r="T8" t="n">
-        <v>1.244</v>
+        <v>0.0162</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4442</v>
+        <v>-0.2059</v>
       </c>
       <c r="V8" t="n">
-        <v>-3.0699</v>
+        <v>-2.0875</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.842</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.0699</v>
+        <v>-3.9295</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.4633</v>
+        <v>-3.2561</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.5779</v>
+        <v>-2.4778</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8854</v>
+        <v>-0.7783</v>
       </c>
       <c r="G9" t="n">
         <v>-2.9993</v>
@@ -1156,13 +1156,13 @@
         <v>0.965</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.464</v>
+        <v>-0.2568</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4019</v>
+        <v>-0.3017</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0621</v>
+        <v>0.0449</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. LINDE GIL</t>
+          <t>A. VASQUEZ BAUTISTA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.0645</v>
+        <v>-3.6873</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3378</v>
+        <v>-0.8899</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.4023</v>
+        <v>-2.7974</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1943</v>
+        <v>-2.1347</v>
       </c>
       <c r="H10" t="n">
-        <v>1.0081</v>
+        <v>-1.3714</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.2024</v>
+        <v>-0.7633</v>
       </c>
       <c r="J10" t="n">
-        <v>1.7941</v>
+        <v>-0.3865</v>
       </c>
       <c r="K10" t="n">
-        <v>2.0233</v>
+        <v>-0.59</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.2291</v>
+        <v>0.2035</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.9884</v>
+        <v>-1.7481</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.0152</v>
+        <v>-0.7813</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9732</v>
+        <v>-0.9668</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.772</v>
+        <v>0.772</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.8951</v>
+        <v>-0.965</v>
       </c>
       <c r="R10" t="n">
-        <v>2.1231</v>
+        <v>1.7371</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0106</v>
+        <v>0.7453</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4032</v>
+        <v>0.4617</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6075</v>
+        <v>0.2835</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.0875</v>
+        <v>-3.0699</v>
       </c>
       <c r="W10" t="n">
-        <v>1.842</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.9295</v>
+        <v>-3.0699</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.1178</v>
+        <v>-5.0419</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.5455</v>
+        <v>-4.068</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5723</v>
+        <v>-0.9739</v>
       </c>
       <c r="G11" t="n">
         <v>-7.2419</v>
@@ -1312,13 +1312,13 @@
         <v>2.7021</v>
       </c>
       <c r="S11" t="n">
-        <v>1.4099</v>
+        <v>0.4858</v>
       </c>
       <c r="T11" t="n">
-        <v>0.7681</v>
+        <v>0.2456</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6418</v>
+        <v>0.2402</v>
       </c>
       <c r="V11" t="n">
         <v>0.9421</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.7782</v>
+        <v>-6.7326</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.9653</v>
+        <v>-3.9465</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.8129</v>
+        <v>-2.7861</v>
       </c>
       <c r="G12" t="n">
         <v>-4.6962</v>
@@ -1390,13 +1390,13 @@
         <v>1.7371</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.31</v>
+        <v>-0.2644</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0912</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2188</v>
+        <v>-0.192</v>
       </c>
       <c r="V12" t="n">
         <v>-0.614</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-19.9226</v>
+        <v>-19.0302</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.902300000000001</v>
+        <v>-6.009999999999998</v>
       </c>
       <c r="F13" t="n">
         <v>-13.0204</v>
@@ -1468,13 +1468,13 @@
         <v>18.3358</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2908</v>
+        <v>1.1831</v>
       </c>
       <c r="T13" t="n">
-        <v>0.05309999999999998</v>
+        <v>0.9454</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2376000000000001</v>
+        <v>0.2378</v>
       </c>
       <c r="V13" t="n">
         <v>-2.6573</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.036</v>
+        <v>7.7213</v>
       </c>
       <c r="E14" t="n">
-        <v>4.4481</v>
+        <v>4.348</v>
       </c>
       <c r="F14" t="n">
-        <v>3.5878</v>
+        <v>3.3733</v>
       </c>
       <c r="G14" t="n">
         <v>2.7914</v>
@@ -1546,13 +1546,13 @@
         <v>2.3161</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3047</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1322</v>
+        <v>0.0321</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1725</v>
+        <v>-0.042</v>
       </c>
       <c r="V14" t="n">
         <v>4.7468</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.5101</v>
+        <v>6.4632</v>
       </c>
       <c r="E15" t="n">
-        <v>5.7088</v>
+        <v>5.6086</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8013</v>
+        <v>0.8545</v>
       </c>
       <c r="G15" t="n">
         <v>6.1456</v>
@@ -1624,13 +1624,13 @@
         <v>1.7371</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4224</v>
+        <v>0.3754</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1917</v>
+        <v>0.0916</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2307</v>
+        <v>0.2839</v>
       </c>
       <c r="V15" t="n">
         <v>0.3281</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.5712</v>
+        <v>3.7652</v>
       </c>
       <c r="E16" t="n">
-        <v>2.7199</v>
+        <v>2.6198</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8512999999999999</v>
+        <v>1.1454</v>
       </c>
       <c r="G16" t="n">
         <v>4.9874</v>
@@ -1702,13 +1702,13 @@
         <v>1.7371</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4865</v>
+        <v>-0.2925</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1917</v>
+        <v>0.0916</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6782</v>
+        <v>-0.3841</v>
       </c>
       <c r="V16" t="n">
         <v>-0.7368</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.452</v>
+        <v>2.9176</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0319</v>
+        <v>1.6313</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4201</v>
+        <v>1.2863</v>
       </c>
       <c r="G17" t="n">
         <v>1.4327</v>
@@ -1780,13 +1780,13 @@
         <v>2.3161</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8613</v>
+        <v>0.3269</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4429</v>
+        <v>0.0423</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4184</v>
+        <v>0.2845</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.9302</v>
+        <v>2.2571</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2613</v>
+        <v>0.5617</v>
       </c>
       <c r="F18" t="n">
-        <v>1.669</v>
+        <v>1.6954</v>
       </c>
       <c r="G18" t="n">
         <v>1.3061</v>
@@ -1858,13 +1858,13 @@
         <v>1.158</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4112</v>
+        <v>-0.0843</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3569</v>
+        <v>-0.0565</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0542</v>
+        <v>-0.0278</v>
       </c>
       <c r="V18" t="n">
         <v>-0.1228</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.6994</v>
+        <v>1.974</v>
       </c>
       <c r="E19" t="n">
-        <v>3.1691</v>
+        <v>3.0689</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.4696</v>
+        <v>-1.0949</v>
       </c>
       <c r="G19" t="n">
         <v>2.586</v>
@@ -1936,13 +1936,13 @@
         <v>1.3511</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1375</v>
+        <v>0.1372</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0462</v>
+        <v>-0.1464</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0912</v>
+        <v>0.2835</v>
       </c>
       <c r="V19" t="n">
         <v>-0.9421</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.4709</v>
+        <v>1.4104</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0853</v>
+        <v>0.0149</v>
       </c>
       <c r="F20" t="n">
-        <v>1.5562</v>
+        <v>1.3956</v>
       </c>
       <c r="G20" t="n">
         <v>-0.3189</v>
@@ -2014,13 +2014,13 @@
         <v>2.1231</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5618</v>
+        <v>0.5014</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1057</v>
+        <v>-0.0056</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6676</v>
+        <v>0.507</v>
       </c>
       <c r="V20" t="n">
         <v>1.228</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.249</v>
+        <v>1.129</v>
       </c>
       <c r="E21" t="n">
-        <v>1.3173</v>
+        <v>1.117</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0683</v>
+        <v>0.012</v>
       </c>
       <c r="G21" t="n">
         <v>-0.9265</v>
@@ -2092,13 +2092,13 @@
         <v>0.579</v>
       </c>
       <c r="S21" t="n">
-        <v>0.08260000000000001</v>
+        <v>-0.0373</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4297</v>
+        <v>0.2294</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.347</v>
+        <v>-0.2667</v>
       </c>
       <c r="V21" t="n">
         <v>1.5138</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0432</v>
+        <v>0.2769</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7803</v>
+        <v>-0.6802</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8235</v>
+        <v>0.9571</v>
       </c>
       <c r="G22" t="n">
         <v>2.1298</v>
@@ -2170,13 +2170,13 @@
         <v>1.158</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5777</v>
+        <v>-0.3441</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2974</v>
+        <v>-0.1973</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2803</v>
+        <v>-0.1468</v>
       </c>
       <c r="V22" t="n">
         <v>-0.7368</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. PÉREZ DE SAN ROMÁN</t>
+          <t>J. PEREZ BENITO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.883</v>
+        <v>-1.5286</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.0633</v>
+        <v>-2.592</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8197</v>
+        <v>1.0635</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.0073</v>
+        <v>-1.2726</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.0008</v>
+        <v>-0.3344</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0064</v>
+        <v>-0.9382</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6469</v>
+        <v>-1.2731</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6469</v>
+        <v>-0.6212</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>-0.6519</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.3604</v>
+        <v>0.0005</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.3539</v>
+        <v>0.2868</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.0064</v>
+        <v>-0.2863</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.579</v>
+        <v>0.579</v>
       </c>
       <c r="Q23" t="n">
         <v>-0.965</v>
       </c>
       <c r="R23" t="n">
-        <v>0.386</v>
+        <v>1.5441</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3173</v>
+        <v>-0.4263</v>
       </c>
       <c r="T23" t="n">
-        <v>0.5486</v>
+        <v>-0.3539</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2313</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.614</v>
+        <v>-0.4087</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.614</v>
+        <v>-0.4087</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. PEREZ BENITO</t>
+          <t>D. PÉREZ DE SAN ROMÁN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.0164</v>
+        <v>-2.1299</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.8925</v>
+        <v>-1.3637</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8761</v>
+        <v>-0.7661</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.2726</v>
+        <v>-1.0073</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.3344</v>
+        <v>-1.0008</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.9382</v>
+        <v>-0.0064</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.2731</v>
+        <v>-0.6469</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.6212</v>
+        <v>-0.6469</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6519</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.0005</v>
+        <v>-0.3604</v>
       </c>
       <c r="N24" t="n">
-        <v>0.2868</v>
+        <v>-0.3539</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.2863</v>
+        <v>-0.0064</v>
       </c>
       <c r="P24" t="n">
-        <v>0.579</v>
+        <v>-0.579</v>
       </c>
       <c r="Q24" t="n">
         <v>-0.965</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5441</v>
+        <v>0.386</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9142</v>
+        <v>0.0704</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6544</v>
+        <v>0.2482</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2598</v>
+        <v>-0.1778</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.4087</v>
+        <v>-0.614</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.4087</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.14</v>
+        <v>-3.6661</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.8145</v>
+        <v>-1.3138</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.3255</v>
+        <v>-2.3523</v>
       </c>
       <c r="G25" t="n">
         <v>0.6674</v>
@@ -2404,13 +2404,13 @@
         <v>0.965</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.314</v>
+        <v>0.16</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.7139</v>
+        <v>-0.2131</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3999</v>
+        <v>0.3731</v>
       </c>
       <c r="V25" t="n">
         <v>-1.5983</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>19.9226</v>
+        <v>20.5901</v>
       </c>
       <c r="E26" t="n">
         <v>13.0205</v>
       </c>
       <c r="F26" t="n">
-        <v>6.902199999999999</v>
+        <v>7.569800000000001</v>
       </c>
       <c r="G26" t="n">
         <v>18.5211</v>
@@ -2482,13 +2482,13 @@
         <v>17.3707</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.291</v>
+        <v>0.3769</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.2376999999999997</v>
+        <v>-0.2376000000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.0529</v>
+        <v>0.6143999999999998</v>
       </c>
       <c r="V26" t="n">
         <v>2.657200000000001</v>
